--- a/mps-nivel-c/oficial/04_registros/PROFARMA_Cadastro-de-Clientes/GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx
+++ b/mps-nivel-c/oficial/04_registros/PROFARMA_Cadastro-de-Clientes/GEST-PROFARMA01_Planilha-de-Gestao-do-Projeto.xlsx
@@ -659,24 +659,24 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>Tech Lead / Arquiteto</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Tiago Nascimento</t>
+          <t>Cézar Hiraki Velázquez</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Dev Principal / Arquiteto</t>
+          <t>Dev Backend (sênior)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Erick Coelho</t>
+          <t>Mateus Veloso</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>CR-08; Cézar Hiraki entra no squad</t>
+          <t>CR-08 (métricas Prometheus /metrics)</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Tiago Nascimento — Tech Lead</t>
+          <t>Cézar Hiraki Velázquez — Tech Lead / Arquiteto</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Decisões técnicas, PRs críticos, arquitetura</t>
+          <t>Arquitetura da solução, decisões técnicas, DevOps/CI, PRs críticos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -7174,24 +7174,24 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Integral</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3 integrais (Sp 1–19)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Parcial — suporte estratégico</t>
+          <t>Tech Lead técnico</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Erick Coelho — Dev Principal / Arquiteto</t>
+          <t>Mateus Veloso — Dev Backend</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -7201,12 +7201,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Arquitetura da solução, endpoints core, integrações principais</t>
+          <t>Desenvolvimento backend, endpoints core, rastreabilidade de tickets</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>1–11</t>
+          <t>1–19</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -7216,19 +7216,15 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>3 devs (Sp 1–7)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Saiu após Sprint 11</t>
-        </is>
-      </c>
+          <t>3 integrais (Sp 1–19)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Gustavo Mathias — Dev Backend</t>
+          <t>Raony Chagas — Dev Backend</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -7238,7 +7234,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Desenvolvimento backend, rastreabilidade de tickets</t>
+          <t>Desenvolvimento backend, integrações, PRs finais</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -7253,15 +7249,15 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>3 devs (Sp 1–7)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr"/>
+          <t>3 integrais (Sp 1–19)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Renan Kiyoshi — Dev Backend</t>
+          <t>Lucas Batista — Dev Backend</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -7271,30 +7267,34 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Desenvolvimento backend, PRs finais</t>
+          <t>Desenvolvimento backend, suporte e PRs finais</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>1–19</t>
+          <t>13–19</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Integral</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>3 devs (Sp 1–7)</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Entrou no Sprint 13</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Cézar Hiraki — Dev Backend</t>
+          <t>Caroline Sousa — QA / Automação</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -7304,34 +7304,34 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Desenvolvimento backend fase final</t>
+          <t>Testes automatizados, apoio à homologação</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>8–19</t>
+          <t>15–19</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Integral</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>4 devs (Sp 8+)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Squad passou para 4 devs no Sprint 8</t>
+          <t>Entrou no Sprint 15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>João Cruz — Dev Backend</t>
+          <t>Jonathan Barbosa — GQA</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -7341,17 +7341,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Suporte ao desenvolvimento</t>
+          <t>Auditor de processo (GQA) — independente da equipe de execução</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>13–19</t>
+          <t>Auditorias</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Estratégico</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7361,116 +7361,36 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>3 auditorias realizadas</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>David Buena — Infra / DevOps</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Timeware</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Proposta de infraestrutura Azure produtiva</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Sprint 14 apenas</t>
-        </is>
-      </c>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="7" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Lucas Batista — QA / Automação</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Timeware</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Testes automatizados</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>15–19</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>COO (Operações)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Timeware</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Auditor GQA — independente da equipe de execução</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Auditorias</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Estratégico</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>3 auditorias realizadas</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -7519,7 +7439,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>3 (Erick, Gustavo, Renan)</t>
+          <t>3 (Cézar, Mateus, Raony)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -7542,7 +7462,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 (Cézar, Mateus, Raony)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -7565,7 +7485,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>4 (Cézar entra no Sprint 8)</t>
+          <t>3 (Cézar, Mateus, Raony)</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -7573,11 +7493,7 @@
           <t>~32 SP/sprint</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Aumento de capacidade</t>
-        </is>
-      </c>
+      <c r="E19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -7592,7 +7508,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3 + Lucas (parcial, Sprint 13)</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -7619,7 +7535,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>4 + João Cruz parcial</t>
+          <t>3 + Lucas + Caroline (QA, Sprint 15)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -7642,7 +7558,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>4 + João Cruz parcial</t>
+          <t>3 + Lucas + Caroline (parciais)</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -8436,7 +8352,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>32</v>
@@ -8460,7 +8376,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Cézar Hiraki entra (capacity +1). CR-08</t>
+          <t>CR-08 (métricas Prometheus /metrics)</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8392,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="8" t="n">
         <v>28</v>
@@ -8516,7 +8432,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>30</v>
@@ -8556,7 +8472,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>28</v>
@@ -8596,7 +8512,7 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="18" t="n">
         <v>28</v>
@@ -8636,7 +8552,7 @@
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>28</v>
@@ -8676,7 +8592,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>28</v>
@@ -8716,7 +8632,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="8" t="n">
         <v>32</v>
@@ -8756,7 +8672,7 @@
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>35</v>
@@ -8796,7 +8712,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" s="8" t="n">
         <v>32</v>
@@ -8836,7 +8752,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="10" t="n">
         <v>28</v>
@@ -8876,7 +8792,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="8" t="n">
         <v>30</v>
@@ -11283,7 +11199,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Referência: GQA-PROFARMA01-001 · EST-GPC-001 · Auditor: COO (Operações) — independente da equipe de projeto</t>
+          <t>Referência: GQA-PROFARMA01-001 · EST-GPC-001 · Auditor: Jonathan Barbosa — independente da equipe de projeto</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11211,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>COO (Operações)</t>
+          <t>Jonathan Barbosa</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11223,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Sim — COO não participa da execução do projeto</t>
+          <t>Sim — Jonathan Barbosa não participa da execução do projeto</t>
         </is>
       </c>
     </row>
